--- a/public/templates/catalog-import-03.xlsx
+++ b/public/templates/catalog-import-03.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R2c35ac90410142df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_套筒" sheetId="2" r:id="Rc4cb765474f44991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R88a8c74273224fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R80bf22f9008a4b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R7f5533968bc0402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_套筒" sheetId="2" r:id="R8f0571d9fad94d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R2d8404176a774230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Rf0e1d6d622e8414e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>

--- a/public/templates/catalog-import-03.xlsx
+++ b/public/templates/catalog-import-03.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R7f5533968bc0402c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_套筒" sheetId="2" r:id="R8f0571d9fad94d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R2d8404176a774230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Rf0e1d6d622e8414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rfebd2ea9368149c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_套筒" sheetId="2" r:id="R8590e1ed8d8c43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R5602a4b3837e4778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R02b8d6be3a304270"/>
   </x:sheets>
 </x:workbook>
 </file>
